--- a/xlsx/tests/templates/crossword.xlsx
+++ b/xlsx/tests/templates/crossword.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E370D1-4339-2A49-B764-A6CF3A9BFDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744B4130-4EE6-EA49-BB57-2DC3BCC1B1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-18780" windowWidth="34220" windowHeight="17260" xr2:uid="{2706468E-7EAE-D749-B249-51B331F89E88}"/>
   </bookViews>
   <sheets>
     <sheet name="Crossword" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -28,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -56,7 +62,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="40">
+  <si>
+    <t>HOW THIS CROSSWORD WORKS</t>
+  </si>
+  <si>
+    <t>• Type ONE letter per white square in the grid below. Clues are on the right side.</t>
+  </si>
+  <si>
+    <t>• Correct letters turn GREEN automatically; wrong letters turn RED.</t>
+  </si>
+  <si>
+    <t>• Track your progress on the right. The answer key lives on the hidden 'Key' sheet.</t>
+  </si>
+  <si>
+    <t>CROSSWORD ▣ Spreadsheet Edition</t>
+  </si>
+  <si>
+    <t>Answer key (mirrors sheet Crossword grid B8:J17)</t>
+  </si>
   <si>
     <t>#</t>
   </si>
@@ -115,9 +139,39 @@
     <t>Across</t>
   </si>
   <si>
+    <t>C9. The data a cell holds (5)</t>
+  </si>
+  <si>
+    <t>E11. Show only rows that meet a condition (6)</t>
+  </si>
+  <si>
+    <t>B13. The arithmetic mean (7)</t>
+  </si>
+  <si>
+    <t>B15. A vertical line of cells, A or B (6)</t>
+  </si>
+  <si>
+    <t>D17. Structured range with headers (5)</t>
+  </si>
+  <si>
     <t>Down</t>
   </si>
   <si>
+    <t>G8. A single box in the grid (4)</t>
+  </si>
+  <si>
+    <t>E11. An expression starting with = (7)</t>
+  </si>
+  <si>
+    <t>J11. A selection of cells, e.g. A1:B5 (5)</t>
+  </si>
+  <si>
+    <t>B12. Find a value's position (lookup) (5)</t>
+  </si>
+  <si>
+    <t>Keep going...</t>
+  </si>
+  <si>
     <t>Progress</t>
   </si>
   <si>
@@ -128,58 +182,13 @@
   </si>
   <si>
     <t>Complete:</t>
-  </si>
-  <si>
-    <t>CROSSWORD ▣ Spreadsheet Edition</t>
-  </si>
-  <si>
-    <t>HOW THIS CROSSWORD WORKS</t>
-  </si>
-  <si>
-    <t>• Type ONE letter per white square in the grid below. Clues are on the right side.</t>
-  </si>
-  <si>
-    <t>• Correct letters turn GREEN automatically; wrong letters turn RED.</t>
-  </si>
-  <si>
-    <t>• Track your progress on the right. The answer key lives on the hidden 'Key' sheet.</t>
-  </si>
-  <si>
-    <t>G8. A single box in the grid (4)</t>
-  </si>
-  <si>
-    <t>E11. An expression starting with = (7)</t>
-  </si>
-  <si>
-    <t>J11. A selection of cells, e.g. A1:B5 (5)</t>
-  </si>
-  <si>
-    <t>B12. Find a value's position (lookup) (5)</t>
-  </si>
-  <si>
-    <t>C9. The data a cell holds (5)</t>
-  </si>
-  <si>
-    <t>E11. Show only rows that meet a condition (6)</t>
-  </si>
-  <si>
-    <t>B13. The arithmetic mean (7)</t>
-  </si>
-  <si>
-    <t>B15. A vertical line of cells, A or B (6)</t>
-  </si>
-  <si>
-    <t>D17. Structured range with headers (5)</t>
-  </si>
-  <si>
-    <t>Answer key (mirrors sheet Crossword grid B8:J17)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -189,10 +198,9 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="16"/>
+      <color rgb="FF92D050"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -200,70 +208,36 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="4"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
-      <color rgb="FF999999"/>
+      <color theme="1" tint="0.499984740745262"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF1F2430"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF1F2430"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="4"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -276,16 +250,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="1" tint="0.249977111117893"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="1" tint="0.249977111117893"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="1" tint="0.249977111117893"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="1" tint="0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -293,49 +267,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FFD21D21"/>
@@ -366,28 +321,16 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFD21D21"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBE7E8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF008121"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF1F6EA"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFBE7E8"/>
+      <color rgb="FFD21D21"/>
+      <color rgb="FF008121"/>
+      <color rgb="FFF1F6EA"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -400,7 +343,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="IronCalc Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="IronCalc">
   <a:themeElements>
     <a:clrScheme name="IronCalc">
       <a:dk1>
@@ -715,250 +658,230 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3013A7C1-D964-3D43-A9E4-35B9778E8A68}">
+  <dimension ref="B1:M25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="11" width="3.83203125" customWidth="1"/>
-    <col min="12" max="13" width="11.1640625" customWidth="1"/>
+    <col min="1" max="11" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="16" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+    <row r="1" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="L8" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="L9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:13" s="2" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+    <row r="10" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="L10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:13" s="2" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="2" t="s">
+    <row r="11" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="L11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:13" s="2" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
+    <row r="12" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="L12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:13" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="L8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="L9" s="2" t="s">
+    <row r="13" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="L13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="L15" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="L16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="L17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L18" t="s">
         <v>33</v>
       </c>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="L10" s="2" t="s">
+    </row>
+    <row r="19" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L19" t="s">
         <v>34</v>
       </c>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="L11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="L12" s="2" t="s">
+    </row>
+    <row r="20" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="L13" s="2" t="s">
+    </row>
+    <row r="22" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L22" t="s">
         <v>37</v>
       </c>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="L15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="L16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="L17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F19" s="8" t="str">
-        <f>IF(M22=M23,"🎉 SOLVED! 🎉","Keep going...")</f>
-        <v>Keep going...</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L21" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="9" cm="1">
+      <c r="M22" s="5" cm="1">
         <f t="array" ref="M22">SUMPRODUCT((Key!B3:J12&lt;&gt;"#")*(UPPER(B8:J17&amp;"")=UPPER(Key!B3:J12&amp;"")))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M23" s="9" cm="1">
+    <row r="23" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L23" t="s">
+        <v>38</v>
+      </c>
+      <c r="M23" s="5" cm="1">
         <f t="array" ref="M23">SUMPRODUCT((Key!B3:J12&lt;&gt;"#")*1)</f>
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="L24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M24" s="10">
+    <row r="24" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L24" t="s">
+        <v>39</v>
+      </c>
+      <c r="M24" s="7">
         <f>M22/M23</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="2:13" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <conditionalFormatting sqref="B8:J17">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>B8&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -967,7 +890,20 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="2" id="{00000000-000E-0000-0000-000001000000}">
+          <x14:cfRule type="expression" priority="1" id="{D5887CFA-0DAD-EF42-85E4-43841C32D6E5}">
+            <xm:f>Key!B3="#"</xm:f>
+            <x14:dxf>
+              <font>
+                <color theme="1"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="2" stopIfTrue="1" id="{4E0BECEB-A57B-D249-BC5C-464FB2372810}">
             <xm:f>UPPER(B8)=UPPER(Key!B3)</xm:f>
             <x14:dxf>
               <font>
@@ -976,19 +912,6 @@
               <fill>
                 <patternFill>
                   <bgColor rgb="FFF1F6EA"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="1" stopIfTrue="1" id="{00000000-000E-0000-0000-000003000000}">
-            <xm:f>Key!B3="#"</xm:f>
-            <x14:dxf>
-              <font>
-                <color theme="1"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="1"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -1002,308 +925,310 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:J12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37BC4D0B-A798-5B4B-8526-6305D5F685C2}">
+  <dimension ref="B1:J13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="11" width="3.83203125" customWidth="1"/>
+    <col min="1" max="11" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
         <v>9</v>
       </c>
-      <c r="I6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="H12" t="s">
         <v>12</v>
       </c>
-      <c r="F7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" t="s">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>0</v>
-      </c>
-      <c r="I10" t="s">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" t="s">
-        <v>6</v>
-      </c>
       <c r="I12" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12" t="s">
-        <v>0</v>
-      </c>
-    </row>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
